--- a/Data/Rules/Aroma Paws Rules Matrix.xlsx
+++ b/Data/Rules/Aroma Paws Rules Matrix.xlsx
@@ -883,7 +883,7 @@
         <v>2</v>
       </c>
       <c r="AE2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF2" t="b">
         <v>0</v>
@@ -1005,7 +1005,7 @@
         <v>2</v>
       </c>
       <c r="AE3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF3" t="b">
         <v>0</v>
@@ -1124,10 +1124,10 @@
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AF4" t="b">
         <v>0</v>
@@ -1171,103 +1171,103 @@
         <v>1</v>
       </c>
       <c r="E5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="b">
         <v>1</v>
@@ -1371,7 +1371,7 @@
         <v>2</v>
       </c>
       <c r="AE6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF6" t="b">
         <v>0</v>
@@ -1493,7 +1493,7 @@
         <v>2</v>
       </c>
       <c r="AE7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF7" t="b">
         <v>0</v>
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="AE8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF8" t="b">
         <v>0</v>
@@ -1659,103 +1659,103 @@
         <v>1</v>
       </c>
       <c r="E9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="b">
         <v>1</v>
@@ -1856,10 +1856,10 @@
         <v>0</v>
       </c>
       <c r="AD10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AF10" t="b">
         <v>0</v>
@@ -1903,103 +1903,103 @@
         <v>1</v>
       </c>
       <c r="E11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="b">
         <v>1</v>
@@ -2100,10 +2100,10 @@
         <v>0</v>
       </c>
       <c r="AD12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE12">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AF12" t="b">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>2</v>
       </c>
       <c r="AE13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF13" t="b">
         <v>0</v>
@@ -2347,7 +2347,7 @@
         <v>2</v>
       </c>
       <c r="AE14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF14" t="b">
         <v>0</v>
@@ -2391,103 +2391,103 @@
         <v>1</v>
       </c>
       <c r="E15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="b">
         <v>1</v>
@@ -2588,10 +2588,10 @@
         <v>0</v>
       </c>
       <c r="AD16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE16">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AF16" t="b">
         <v>0</v>
@@ -2713,7 +2713,7 @@
         <v>2</v>
       </c>
       <c r="AE17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF17" t="b">
         <v>0</v>
@@ -2757,103 +2757,103 @@
         <v>1</v>
       </c>
       <c r="E18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="b">
         <v>1</v>
@@ -2957,7 +2957,7 @@
         <v>2</v>
       </c>
       <c r="AE19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF19" t="b">
         <v>0</v>
@@ -3001,103 +3001,103 @@
         <v>1</v>
       </c>
       <c r="E20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M20">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V20">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y20">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH20">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK20">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="b">
         <v>1</v>
@@ -3201,7 +3201,7 @@
         <v>2</v>
       </c>
       <c r="AE21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF21" t="b">
         <v>0</v>
@@ -3245,103 +3245,103 @@
         <v>1</v>
       </c>
       <c r="E22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="b">
         <v>1</v>
@@ -3445,7 +3445,7 @@
         <v>2</v>
       </c>
       <c r="AE23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF23" t="b">
         <v>0</v>
@@ -3567,7 +3567,7 @@
         <v>2</v>
       </c>
       <c r="AE24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF24" t="b">
         <v>0</v>
@@ -3689,7 +3689,7 @@
         <v>2</v>
       </c>
       <c r="AE25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF25" t="b">
         <v>0</v>
@@ -3811,7 +3811,7 @@
         <v>2</v>
       </c>
       <c r="AE26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF26" t="b">
         <v>0</v>
@@ -3855,103 +3855,103 @@
         <v>1</v>
       </c>
       <c r="E27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J27">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M27">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V27">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y27">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH27">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK27">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="b">
         <v>1</v>
@@ -4055,7 +4055,7 @@
         <v>2</v>
       </c>
       <c r="AE28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF28" t="b">
         <v>0</v>
@@ -4221,103 +4221,103 @@
         <v>1</v>
       </c>
       <c r="E30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="b">
         <v>1</v>
@@ -4418,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="AD31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE31">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AF31" t="b">
         <v>0</v>
@@ -4543,7 +4543,7 @@
         <v>2</v>
       </c>
       <c r="AE32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF32" t="b">
         <v>0</v>
@@ -4662,10 +4662,10 @@
         <v>0</v>
       </c>
       <c r="AD33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE33">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AF33" t="b">
         <v>0</v>
@@ -4787,7 +4787,7 @@
         <v>2</v>
       </c>
       <c r="AE34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF34" t="b">
         <v>0</v>

--- a/Data/Rules/Aroma Paws Rules Matrix.xlsx
+++ b/Data/Rules/Aroma Paws Rules Matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="108">
   <si>
     <t>SKU</t>
   </si>
@@ -134,6 +134,9 @@
   </si>
   <si>
     <t>HQ_Max</t>
+  </si>
+  <si>
+    <t>Total Max</t>
   </si>
   <si>
     <t>11922</t>
@@ -666,10 +669,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AN34"/>
+  <dimension ref="A1:AO34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:40">
+    <row r="1" spans="1:41">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -790,16 +793,19 @@
       <c r="AN1" t="s">
         <v>39</v>
       </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="2" spans="1:40">
+    <row r="2" spans="1:41">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -912,16 +918,19 @@
       <c r="AN2">
         <v>0</v>
       </c>
+      <c r="AO2">
+        <v>29</v>
+      </c>
     </row>
-    <row r="3" spans="1:40">
+    <row r="3" spans="1:41">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1034,16 +1043,19 @@
       <c r="AN3">
         <v>0</v>
       </c>
+      <c r="AO3">
+        <v>29</v>
+      </c>
     </row>
-    <row r="4" spans="1:40">
+    <row r="4" spans="1:41">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1156,16 +1168,19 @@
       <c r="AN4">
         <v>0</v>
       </c>
+      <c r="AO4">
+        <v>32</v>
+      </c>
     </row>
-    <row r="5" spans="1:40">
+    <row r="5" spans="1:41">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1278,16 +1293,19 @@
       <c r="AN5">
         <v>0</v>
       </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:40">
+    <row r="6" spans="1:41">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1400,16 +1418,19 @@
       <c r="AN6">
         <v>0</v>
       </c>
+      <c r="AO6">
+        <v>29</v>
+      </c>
     </row>
-    <row r="7" spans="1:40">
+    <row r="7" spans="1:41">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1522,16 +1543,19 @@
       <c r="AN7">
         <v>0</v>
       </c>
+      <c r="AO7">
+        <v>29</v>
+      </c>
     </row>
-    <row r="8" spans="1:40">
+    <row r="8" spans="1:41">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1644,16 +1668,19 @@
       <c r="AN8">
         <v>0</v>
       </c>
+      <c r="AO8">
+        <v>29</v>
+      </c>
     </row>
-    <row r="9" spans="1:40">
+    <row r="9" spans="1:41">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1766,16 +1793,19 @@
       <c r="AN9">
         <v>0</v>
       </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:40">
+    <row r="10" spans="1:41">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1888,16 +1918,19 @@
       <c r="AN10">
         <v>0</v>
       </c>
+      <c r="AO10">
+        <v>31</v>
+      </c>
     </row>
-    <row r="11" spans="1:40">
+    <row r="11" spans="1:41">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -2010,16 +2043,19 @@
       <c r="AN11">
         <v>0</v>
       </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:40">
+    <row r="12" spans="1:41">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -2132,16 +2168,19 @@
       <c r="AN12">
         <v>0</v>
       </c>
+      <c r="AO12">
+        <v>31</v>
+      </c>
     </row>
-    <row r="13" spans="1:40">
+    <row r="13" spans="1:41">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -2254,16 +2293,19 @@
       <c r="AN13">
         <v>0</v>
       </c>
+      <c r="AO13">
+        <v>29</v>
+      </c>
     </row>
-    <row r="14" spans="1:40">
+    <row r="14" spans="1:41">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -2376,16 +2418,19 @@
       <c r="AN14">
         <v>0</v>
       </c>
+      <c r="AO14">
+        <v>29</v>
+      </c>
     </row>
-    <row r="15" spans="1:40">
+    <row r="15" spans="1:41">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -2498,16 +2543,19 @@
       <c r="AN15">
         <v>0</v>
       </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40">
+    <row r="16" spans="1:41">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -2620,16 +2668,19 @@
       <c r="AN16">
         <v>0</v>
       </c>
+      <c r="AO16">
+        <v>31</v>
+      </c>
     </row>
-    <row r="17" spans="1:40">
+    <row r="17" spans="1:41">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -2742,16 +2793,19 @@
       <c r="AN17">
         <v>0</v>
       </c>
+      <c r="AO17">
+        <v>29</v>
+      </c>
     </row>
-    <row r="18" spans="1:40">
+    <row r="18" spans="1:41">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -2864,16 +2918,19 @@
       <c r="AN18">
         <v>0</v>
       </c>
+      <c r="AO18">
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" spans="1:40">
+    <row r="19" spans="1:41">
       <c r="A19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -2986,16 +3043,19 @@
       <c r="AN19">
         <v>0</v>
       </c>
+      <c r="AO19">
+        <v>29</v>
+      </c>
     </row>
-    <row r="20" spans="1:40">
+    <row r="20" spans="1:41">
       <c r="A20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -3108,16 +3168,19 @@
       <c r="AN20">
         <v>0</v>
       </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="1:40">
+    <row r="21" spans="1:41">
       <c r="A21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -3230,16 +3293,19 @@
       <c r="AN21">
         <v>0</v>
       </c>
+      <c r="AO21">
+        <v>29</v>
+      </c>
     </row>
-    <row r="22" spans="1:40">
+    <row r="22" spans="1:41">
       <c r="A22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -3352,16 +3418,19 @@
       <c r="AN22">
         <v>0</v>
       </c>
+      <c r="AO22">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="1:40">
+    <row r="23" spans="1:41">
       <c r="A23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -3474,16 +3543,19 @@
       <c r="AN23">
         <v>0</v>
       </c>
+      <c r="AO23">
+        <v>29</v>
+      </c>
     </row>
-    <row r="24" spans="1:40">
+    <row r="24" spans="1:41">
       <c r="A24" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -3596,16 +3668,19 @@
       <c r="AN24">
         <v>0</v>
       </c>
+      <c r="AO24">
+        <v>29</v>
+      </c>
     </row>
-    <row r="25" spans="1:40">
+    <row r="25" spans="1:41">
       <c r="A25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -3718,16 +3793,19 @@
       <c r="AN25">
         <v>0</v>
       </c>
+      <c r="AO25">
+        <v>29</v>
+      </c>
     </row>
-    <row r="26" spans="1:40">
+    <row r="26" spans="1:41">
       <c r="A26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C26" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -3840,16 +3918,19 @@
       <c r="AN26">
         <v>0</v>
       </c>
+      <c r="AO26">
+        <v>29</v>
+      </c>
     </row>
-    <row r="27" spans="1:40">
+    <row r="27" spans="1:41">
       <c r="A27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C27" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -3962,16 +4043,19 @@
       <c r="AN27">
         <v>0</v>
       </c>
+      <c r="AO27">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="1:40">
+    <row r="28" spans="1:41">
       <c r="A28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C28" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -4084,16 +4168,19 @@
       <c r="AN28">
         <v>0</v>
       </c>
+      <c r="AO28">
+        <v>29</v>
+      </c>
     </row>
-    <row r="29" spans="1:40">
+    <row r="29" spans="1:41">
       <c r="A29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -4206,16 +4293,19 @@
       <c r="AN29">
         <v>0</v>
       </c>
+      <c r="AO29">
+        <v>28</v>
+      </c>
     </row>
-    <row r="30" spans="1:40">
+    <row r="30" spans="1:41">
       <c r="A30" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C30" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -4328,16 +4418,19 @@
       <c r="AN30">
         <v>0</v>
       </c>
+      <c r="AO30">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="1:40">
+    <row r="31" spans="1:41">
       <c r="A31" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B31" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C31" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -4450,16 +4543,19 @@
       <c r="AN31">
         <v>0</v>
       </c>
+      <c r="AO31">
+        <v>31</v>
+      </c>
     </row>
-    <row r="32" spans="1:40">
+    <row r="32" spans="1:41">
       <c r="A32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B32" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C32" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -4572,16 +4668,19 @@
       <c r="AN32">
         <v>0</v>
       </c>
+      <c r="AO32">
+        <v>29</v>
+      </c>
     </row>
-    <row r="33" spans="1:40">
+    <row r="33" spans="1:41">
       <c r="A33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C33" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -4694,16 +4793,19 @@
       <c r="AN33">
         <v>0</v>
       </c>
+      <c r="AO33">
+        <v>31</v>
+      </c>
     </row>
-    <row r="34" spans="1:40">
+    <row r="34" spans="1:41">
       <c r="A34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C34" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -4815,6 +4917,9 @@
       </c>
       <c r="AN34">
         <v>0</v>
+      </c>
+      <c r="AO34">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
